--- a/test/inputs/case6/case6.xlsx
+++ b/test/inputs/case6/case6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nomyk\Desktop\Network Reduction Model\NetworkReduction.jl\test\inputs\case6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35620FAF-A6F5-4E24-8611-5956903AE06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA16129-E806-46BF-9B86-113134FAA536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
   <si>
     <t>Line_name</t>
   </si>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>Cost</t>
+  </si>
+  <si>
+    <t>IsRepresentative</t>
   </si>
 </sst>
 </file>
@@ -878,69 +881,70 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21614AC-DED9-4872-B6E6-60BCE42766DA}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -952,42 +956,42 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
         <v>1.05</v>
       </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
       <c r="J2">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>230</v>
       </c>
       <c r="L2">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -999,42 +1003,42 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>1.05</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
       <c r="J3">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>230</v>
       </c>
       <c r="L3">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1046,171 +1050,174 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
         <v>1.07</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
       <c r="J4">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="K4">
+        <v>230</v>
+      </c>
+      <c r="L4">
         <v>2</v>
-      </c>
-      <c r="L4">
-        <v>1.07</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
       <c r="C5">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>70</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="K5">
+        <v>230</v>
+      </c>
+      <c r="L5">
         <v>2</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>1.05</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>0.95</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
       <c r="O5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
       <c r="C6">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>70</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="K6">
+        <v>230</v>
+      </c>
+      <c r="L6">
         <v>3</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>1.05</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.95</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
       <c r="O6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
       <c r="C7">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>70</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="K7">
+        <v>230</v>
+      </c>
+      <c r="L7">
         <v>3</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>1.05</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.95</v>
       </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
       <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
         <v>0</v>
       </c>
     </row>

--- a/test/inputs/case6/case6.xlsx
+++ b/test/inputs/case6/case6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nomyk\Desktop\Network Reduction Model\NetworkReduction.jl\test\inputs\case6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA16129-E806-46BF-9B86-113134FAA536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35620FAF-A6F5-4E24-8611-5956903AE06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <si>
     <t>Line_name</t>
   </si>
@@ -136,9 +136,6 @@
   </si>
   <si>
     <t>Cost</t>
-  </si>
-  <si>
-    <t>IsRepresentative</t>
   </si>
 </sst>
 </file>
@@ -881,70 +878,69 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21614AC-DED9-4872-B6E6-60BCE42766DA}">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:15">
       <c r="A1" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="P1" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -956,42 +952,42 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>230</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
         <v>1.05</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>230</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1003,42 +999,42 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>230</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
         <v>1.05</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>230</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1050,174 +1046,171 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>230</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+      <c r="L4">
         <v>1.07</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>230</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
       </c>
       <c r="M4">
         <v>1.07</v>
       </c>
       <c r="N4">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>4</v>
       </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
       <c r="C5">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="D5">
         <v>70</v>
       </c>
       <c r="E5">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="K5">
-        <v>230</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>1.05</v>
       </c>
       <c r="M5">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="N5">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>5</v>
       </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
       <c r="C6">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="D6">
         <v>70</v>
       </c>
       <c r="E6">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="K6">
-        <v>230</v>
+        <v>3</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>1.05</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="N6">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>6</v>
       </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
       <c r="C7">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="D7">
         <v>70</v>
       </c>
       <c r="E7">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="K7">
-        <v>230</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>1.05</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="N7">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
         <v>0</v>
       </c>
     </row>
